--- a/customer_satisfaction_evaluation_forms/017_customer_satisfaction_survey_quotation_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/017_customer_satisfaction_survey_quotation_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_1</t>
+          <t>how_likely_recommmend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation</t>
+          <t>How likely are you to recommend our service?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_2</t>
+          <t>reason_last_interaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_label</t>
+          <t>Reason for your last interaction with our service</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_3</t>
+          <t>satisfaction_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation</t>
+          <t>On a scale of 0-10, how satisfied are you with our service?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_4</t>
+          <t>favorite_aspects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form</t>
+          <t>What aspects of our service do you enjoy the most?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_5</t>
+          <t>issue_example</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form</t>
+          <t>Example of where you experienced an issue with our service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_6</t>
+          <t>likely_return</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation</t>
+          <t>How likely are you to return to our service in the future?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_7</t>
+          <t>improvement_points</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form</t>
+          <t>What do you think we could do to improve our service?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +681,110 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_8</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation</t>
+          <t>Do you have any comments about your experience with our service?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reason_initial_contact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Why did you contact us initially?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>overall_experience</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>On a scale of 1-5, how would you rate your overall experience?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>communication_quality</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How would you rate the quality of our communication?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>quick_support</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How quickly were you able to get help when you needed it?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,34 +827,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_5_choices</t>
+          <t>likely_return_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_satisfaction_survey_quotation_form_5_choices</t>
+          <t>likely_return_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>likely_return_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Not likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>likely_return_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>not_at_all_likely</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Not at all likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>communication_quality_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>communication_quality_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>communication_quality_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>communication_quality_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>quick_support_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>instantly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>quick_support_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>within_a_few_minutes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Within a few minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quick_support_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>within_a_few_hours</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Within a few hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quick_support_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_quickly_enough</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not quickly enough</t>
         </is>
       </c>
     </row>
